--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.30814590485997</v>
+        <v>5.087573709539745</v>
       </c>
       <c r="D2" t="n">
-        <v>24.43767583056949</v>
+        <v>3.971122322467542</v>
       </c>
       <c r="E2" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F2" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.26217403865506</v>
+        <v>7.355103281281448</v>
       </c>
       <c r="D3" t="n">
-        <v>41.42713783189951</v>
+        <v>6.73190989768367</v>
       </c>
       <c r="E3" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F3" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.32064119353463</v>
+        <v>4.764604193949378</v>
       </c>
       <c r="D4" t="n">
-        <v>26.72264956923247</v>
+        <v>4.342430555000276</v>
       </c>
       <c r="E4" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F4" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.24397696094696</v>
+        <v>5.402146256153881</v>
       </c>
       <c r="D5" t="n">
-        <v>38.89930539292745</v>
+        <v>6.321137126350711</v>
       </c>
       <c r="E5" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F5" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.05170860161147</v>
+        <v>4.883402647761864</v>
       </c>
       <c r="D6" t="n">
-        <v>18.06239186818844</v>
+        <v>2.935138678580622</v>
       </c>
       <c r="E6" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F6" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.55483012556087</v>
+        <v>6.590159895403642</v>
       </c>
       <c r="D7" t="n">
-        <v>27.01061517651058</v>
+        <v>4.389224966182969</v>
       </c>
       <c r="E7" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F7" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.375185801072872</v>
+        <v>0.5484676926743417</v>
       </c>
       <c r="D8" t="n">
-        <v>41.97502043285962</v>
+        <v>6.820940820339688</v>
       </c>
       <c r="E8" t="n">
-        <v>12.331900014421</v>
+        <v>2.003933752343412</v>
       </c>
       <c r="F8" t="n">
-        <v>8.749657210091303</v>
+        <v>1.421819296639837</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
